--- a/suivi_reseaux_politiques.xlsx
+++ b/suivi_reseaux_politiques.xlsx
@@ -13,7 +13,7 @@
     <sheet name="_donnees_graphiques" sheetId="4" state="hidden" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'DONNEES'!$A$1:$H$61</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -431,12 +431,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$B$3:$B$7</f>
+              <f>'_donnees_graphiques'!$B$3:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -467,12 +467,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$C$3:$C$7</f>
+              <f>'_donnees_graphiques'!$C$3:$C$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -503,12 +503,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$D$3:$D$7</f>
+              <f>'_donnees_graphiques'!$D$3:$D$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -539,12 +539,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$E$3:$E$7</f>
+              <f>'_donnees_graphiques'!$E$3:$E$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -575,12 +575,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$F$3:$F$7</f>
+              <f>'_donnees_graphiques'!$F$3:$F$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -611,12 +611,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$G$3:$G$7</f>
+              <f>'_donnees_graphiques'!$G$3:$G$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -647,12 +647,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$H$3:$H$7</f>
+              <f>'_donnees_graphiques'!$H$3:$H$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -683,12 +683,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$I$3:$I$7</f>
+              <f>'_donnees_graphiques'!$I$3:$I$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -719,12 +719,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$J$3:$J$7</f>
+              <f>'_donnees_graphiques'!$J$3:$J$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -755,12 +755,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$A$3:$A$7</f>
+              <f>'_donnees_graphiques'!$A$3:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$K$3:$K$7</f>
+              <f>'_donnees_graphiques'!$K$3:$K$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -878,12 +878,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$N$3:$N$7</f>
+              <f>'_donnees_graphiques'!$N$3:$N$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -914,12 +914,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$O$3:$O$7</f>
+              <f>'_donnees_graphiques'!$O$3:$O$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -950,12 +950,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$P$3:$P$7</f>
+              <f>'_donnees_graphiques'!$P$3:$P$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -986,12 +986,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Q$3:$Q$7</f>
+              <f>'_donnees_graphiques'!$Q$3:$Q$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1022,12 +1022,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$R$3:$R$7</f>
+              <f>'_donnees_graphiques'!$R$3:$R$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1058,12 +1058,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$S$3:$S$7</f>
+              <f>'_donnees_graphiques'!$S$3:$S$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1094,12 +1094,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$T$3:$T$7</f>
+              <f>'_donnees_graphiques'!$T$3:$T$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1130,12 +1130,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$U$3:$U$7</f>
+              <f>'_donnees_graphiques'!$U$3:$U$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1166,12 +1166,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$V$3:$V$7</f>
+              <f>'_donnees_graphiques'!$V$3:$V$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1202,12 +1202,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$M$3:$M$7</f>
+              <f>'_donnees_graphiques'!$M$3:$M$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$W$3:$W$7</f>
+              <f>'_donnees_graphiques'!$W$3:$W$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1325,12 +1325,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$Z$3:$Z$7</f>
+              <f>'_donnees_graphiques'!$Z$3:$Z$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1361,12 +1361,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AA$3:$AA$7</f>
+              <f>'_donnees_graphiques'!$AA$3:$AA$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1397,12 +1397,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AB$3:$AB$7</f>
+              <f>'_donnees_graphiques'!$AB$3:$AB$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1433,12 +1433,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AC$3:$AC$7</f>
+              <f>'_donnees_graphiques'!$AC$3:$AC$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1469,12 +1469,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AD$3:$AD$7</f>
+              <f>'_donnees_graphiques'!$AD$3:$AD$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1505,12 +1505,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AE$3:$AE$7</f>
+              <f>'_donnees_graphiques'!$AE$3:$AE$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1541,12 +1541,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AF$3:$AF$7</f>
+              <f>'_donnees_graphiques'!$AF$3:$AF$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1577,12 +1577,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AG$3:$AG$7</f>
+              <f>'_donnees_graphiques'!$AG$3:$AG$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1613,12 +1613,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AH$3:$AH$7</f>
+              <f>'_donnees_graphiques'!$AH$3:$AH$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1649,12 +1649,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$Y$3:$Y$7</f>
+              <f>'_donnees_graphiques'!$Y$3:$Y$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AI$3:$AI$7</f>
+              <f>'_donnees_graphiques'!$AI$3:$AI$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1772,12 +1772,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AL$3:$AL$7</f>
+              <f>'_donnees_graphiques'!$AL$3:$AL$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1808,12 +1808,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AM$3:$AM$7</f>
+              <f>'_donnees_graphiques'!$AM$3:$AM$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1844,12 +1844,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AN$3:$AN$7</f>
+              <f>'_donnees_graphiques'!$AN$3:$AN$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1880,12 +1880,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AO$3:$AO$7</f>
+              <f>'_donnees_graphiques'!$AO$3:$AO$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1916,12 +1916,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AP$3:$AP$7</f>
+              <f>'_donnees_graphiques'!$AP$3:$AP$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1952,12 +1952,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AQ$3:$AQ$7</f>
+              <f>'_donnees_graphiques'!$AQ$3:$AQ$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -1988,12 +1988,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AR$3:$AR$7</f>
+              <f>'_donnees_graphiques'!$AR$3:$AR$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2024,12 +2024,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AS$3:$AS$7</f>
+              <f>'_donnees_graphiques'!$AS$3:$AS$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2060,12 +2060,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AT$3:$AT$7</f>
+              <f>'_donnees_graphiques'!$AT$3:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2096,12 +2096,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AK$3:$AK$7</f>
+              <f>'_donnees_graphiques'!$AK$3:$AK$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AU$3:$AU$7</f>
+              <f>'_donnees_graphiques'!$AU$3:$AU$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2219,12 +2219,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AX$3:$AX$7</f>
+              <f>'_donnees_graphiques'!$AX$3:$AX$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2255,12 +2255,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AY$3:$AY$7</f>
+              <f>'_donnees_graphiques'!$AY$3:$AY$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2291,12 +2291,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$AZ$3:$AZ$7</f>
+              <f>'_donnees_graphiques'!$AZ$3:$AZ$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2327,12 +2327,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BA$3:$BA$7</f>
+              <f>'_donnees_graphiques'!$BA$3:$BA$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2363,12 +2363,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BB$3:$BB$7</f>
+              <f>'_donnees_graphiques'!$BB$3:$BB$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2399,12 +2399,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BC$3:$BC$7</f>
+              <f>'_donnees_graphiques'!$BC$3:$BC$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2435,12 +2435,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BD$3:$BD$7</f>
+              <f>'_donnees_graphiques'!$BD$3:$BD$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2471,12 +2471,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BE$3:$BE$7</f>
+              <f>'_donnees_graphiques'!$BE$3:$BE$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2507,12 +2507,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BF$3:$BF$7</f>
+              <f>'_donnees_graphiques'!$BF$3:$BF$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -2543,12 +2543,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'_donnees_graphiques'!$AW$3:$AW$7</f>
+              <f>'_donnees_graphiques'!$AW$3:$AW$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'_donnees_graphiques'!$BG$3:$BG$7</f>
+              <f>'_donnees_graphiques'!$BG$3:$BG$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -3023,7 +3023,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H51"/>
+  <dimension ref="A1:H61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -4448,8 +4448,282 @@
         <v>698673</v>
       </c>
     </row>
+    <row r="52">
+      <c r="A52" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B52" s="17" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C52" s="18" t="n">
+        <v>183000</v>
+      </c>
+      <c r="D52" s="18" t="n">
+        <v>192600</v>
+      </c>
+      <c r="E52" s="18" t="n">
+        <v>91000</v>
+      </c>
+      <c r="F52" s="18" t="n"/>
+      <c r="G52" s="18" t="n">
+        <v>19400</v>
+      </c>
+      <c r="H52" s="19" t="n">
+        <v>486000</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B53" s="21" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C53" s="22" t="n">
+        <v>106000</v>
+      </c>
+      <c r="D53" s="22" t="n">
+        <v>213300</v>
+      </c>
+      <c r="E53" s="22" t="n">
+        <v>118000</v>
+      </c>
+      <c r="F53" s="22" t="n"/>
+      <c r="G53" s="22" t="n">
+        <v>85000</v>
+      </c>
+      <c r="H53" s="23" t="n">
+        <v>522300</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B54" s="17" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C54" s="18" t="n">
+        <v>218000</v>
+      </c>
+      <c r="D54" s="18" t="n">
+        <v>941500</v>
+      </c>
+      <c r="E54" s="18" t="n">
+        <v>266000</v>
+      </c>
+      <c r="F54" s="18" t="n"/>
+      <c r="G54" s="18" t="n"/>
+      <c r="H54" s="19" t="n">
+        <v>1425500</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B55" s="21" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C55" s="22" t="n">
+        <v>462000</v>
+      </c>
+      <c r="D55" s="22" t="n">
+        <v>287000</v>
+      </c>
+      <c r="E55" s="22" t="n">
+        <v>181000</v>
+      </c>
+      <c r="F55" s="22" t="n"/>
+      <c r="G55" s="22" t="n">
+        <v>681700</v>
+      </c>
+      <c r="H55" s="23" t="n">
+        <v>1611700</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B56" s="17" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C56" s="18" t="n">
+        <v>31000</v>
+      </c>
+      <c r="D56" s="18" t="n">
+        <v>205400</v>
+      </c>
+      <c r="E56" s="18" t="n">
+        <v>99000</v>
+      </c>
+      <c r="F56" s="18" t="n"/>
+      <c r="G56" s="18" t="n"/>
+      <c r="H56" s="19" t="n">
+        <v>335400</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B57" s="21" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C57" s="22" t="n">
+        <v>758000</v>
+      </c>
+      <c r="D57" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="E57" s="22" t="n">
+        <v>2100000</v>
+      </c>
+      <c r="F57" s="22" t="n"/>
+      <c r="G57" s="22" t="n">
+        <v>1500000</v>
+      </c>
+      <c r="H57" s="23" t="n">
+        <v>7358000</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B58" s="17" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C58" s="18" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="D58" s="18" t="n">
+        <v>628800</v>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>1200000</v>
+      </c>
+      <c r="F58" s="18" t="n"/>
+      <c r="G58" s="18" t="n">
+        <v>2400000</v>
+      </c>
+      <c r="H58" s="19" t="n">
+        <v>5228800</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B59" s="21" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C59" s="22" t="n">
+        <v>867000</v>
+      </c>
+      <c r="D59" s="22" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="E59" s="22" t="n">
+        <v>1900000</v>
+      </c>
+      <c r="F59" s="22" t="n"/>
+      <c r="G59" s="22" t="n">
+        <v>3000000</v>
+      </c>
+      <c r="H59" s="23" t="n">
+        <v>8367000</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="16" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B60" s="17" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C60" s="18" t="n">
+        <v>637000</v>
+      </c>
+      <c r="D60" s="18" t="n">
+        <v>307800</v>
+      </c>
+      <c r="E60" s="18" t="n">
+        <v>181000</v>
+      </c>
+      <c r="F60" s="18" t="n"/>
+      <c r="G60" s="18" t="n"/>
+      <c r="H60" s="19" t="n">
+        <v>1125800</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B61" s="21" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C61" s="22" t="n">
+        <v>357000</v>
+      </c>
+      <c r="D61" s="22" t="n">
+        <v>136200</v>
+      </c>
+      <c r="E61" s="22" t="n">
+        <v>81000</v>
+      </c>
+      <c r="F61" s="22" t="n"/>
+      <c r="G61" s="22" t="n">
+        <v>85600</v>
+      </c>
+      <c r="H61" s="23" t="n">
+        <v>659800</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:H51"/>
+  <autoFilter ref="A1:H61"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -4461,7 +4735,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K112"/>
+  <dimension ref="A1:K162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -4487,7 +4761,7 @@
     <row r="2">
       <c r="A2" s="25" t="inlineStr">
         <is>
-          <t>Dernier releve : 04/09/2026   -   10 personnalites suivies</t>
+          <t>Dernier releve : 07/09/2026   -   10 personnalites suivies</t>
         </is>
       </c>
     </row>
@@ -4575,20 +4849,16 @@
         </is>
       </c>
       <c r="B7" s="31" t="n">
-        <v>8385000</v>
-      </c>
-      <c r="C7" s="40" t="n">
-        <v>-736</v>
-      </c>
-      <c r="D7" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E7" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>8367000</v>
+      </c>
+      <c r="C7" s="32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="D7" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="E7" s="34" t="n">
+        <v>0.5406189158360553</v>
       </c>
       <c r="F7" s="33" t="inlineStr">
         <is>
@@ -4601,10 +4871,10 @@
         </is>
       </c>
       <c r="H7" s="32" t="n">
-        <v>8859</v>
+        <v>28859</v>
       </c>
       <c r="I7" s="34" t="n">
-        <v>0.165956650451915</v>
+        <v>0.5406189158360553</v>
       </c>
     </row>
     <row r="8">
@@ -4614,20 +4884,16 @@
         </is>
       </c>
       <c r="B8" s="36" t="n">
-        <v>7357258</v>
+        <v>7358000</v>
       </c>
       <c r="C8" s="37" t="n">
-        <v>155</v>
-      </c>
-      <c r="D8" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E8" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>742</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>1214</v>
+      </c>
+      <c r="E8" s="39" t="n">
+        <v>0.02072809216522309</v>
       </c>
       <c r="F8" s="38" t="inlineStr">
         <is>
@@ -4640,10 +4906,10 @@
         </is>
       </c>
       <c r="H8" s="37" t="n">
-        <v>472</v>
+        <v>1214</v>
       </c>
       <c r="I8" s="39" t="n">
-        <v>0.008059027596374335</v>
+        <v>0.02072809216522309</v>
       </c>
     </row>
     <row r="9">
@@ -4653,20 +4919,16 @@
         </is>
       </c>
       <c r="B9" s="31" t="n">
-        <v>5628635</v>
-      </c>
-      <c r="C9" s="32" t="n">
-        <v>169</v>
-      </c>
-      <c r="D9" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E9" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>5228800</v>
+      </c>
+      <c r="C9" s="40" t="n">
+        <v>-399835</v>
+      </c>
+      <c r="D9" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="E9" s="41" t="n">
+        <v>-12.37946678717794</v>
       </c>
       <c r="F9" s="33" t="inlineStr">
         <is>
@@ -4678,11 +4940,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H9" s="32" t="n">
-        <v>168</v>
-      </c>
-      <c r="I9" s="34" t="n">
-        <v>0.005203708137635488</v>
+      <c r="H9" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="I9" s="41" t="n">
+        <v>-12.37946678717794</v>
       </c>
     </row>
     <row r="10">
@@ -4692,20 +4954,16 @@
         </is>
       </c>
       <c r="B10" s="36" t="n">
-        <v>2097928</v>
-      </c>
-      <c r="C10" s="42" t="n">
-        <v>-56</v>
-      </c>
-      <c r="D10" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E10" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>1611700</v>
+      </c>
+      <c r="C10" s="37" t="n">
+        <v>772</v>
+      </c>
+      <c r="D10" s="37" t="n">
+        <v>5618</v>
+      </c>
+      <c r="E10" s="39" t="n">
+        <v>0.6077573989973883</v>
       </c>
       <c r="F10" s="38" t="inlineStr">
         <is>
@@ -4718,10 +4976,10 @@
         </is>
       </c>
       <c r="H10" s="37" t="n">
-        <v>4446</v>
+        <v>5618</v>
       </c>
       <c r="I10" s="39" t="n">
-        <v>0.3150103940676496</v>
+        <v>0.6077573989973883</v>
       </c>
     </row>
     <row r="11">
@@ -4731,20 +4989,16 @@
         </is>
       </c>
       <c r="B11" s="31" t="n">
-        <v>1856425</v>
+        <v>1425500</v>
       </c>
       <c r="C11" s="32" t="n">
-        <v>93</v>
-      </c>
-      <c r="D11" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E11" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>75</v>
+      </c>
+      <c r="D11" s="32" t="n">
+        <v>449</v>
+      </c>
+      <c r="E11" s="34" t="n">
+        <v>0.03150764428780928</v>
       </c>
       <c r="F11" s="33" t="inlineStr">
         <is>
@@ -4757,10 +5011,10 @@
         </is>
       </c>
       <c r="H11" s="32" t="n">
-        <v>1374</v>
+        <v>449</v>
       </c>
       <c r="I11" s="34" t="n">
-        <v>0.07406804449041626</v>
+        <v>0.03150764428780928</v>
       </c>
     </row>
     <row r="12">
@@ -4770,20 +5024,16 @@
         </is>
       </c>
       <c r="B12" s="36" t="n">
-        <v>1124800</v>
+        <v>1125800</v>
       </c>
       <c r="C12" s="37" t="n">
-        <v>117</v>
-      </c>
-      <c r="D12" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E12" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>1000</v>
+      </c>
+      <c r="D12" s="37" t="n">
+        <v>1382</v>
+      </c>
+      <c r="E12" s="39" t="n">
+        <v>0.1229080288647211</v>
       </c>
       <c r="F12" s="38" t="inlineStr">
         <is>
@@ -4796,10 +5046,10 @@
         </is>
       </c>
       <c r="H12" s="37" t="n">
-        <v>382</v>
+        <v>1382</v>
       </c>
       <c r="I12" s="39" t="n">
-        <v>0.03397313098865151</v>
+        <v>0.1229080288647211</v>
       </c>
     </row>
     <row r="13">
@@ -4809,20 +5059,16 @@
         </is>
       </c>
       <c r="B13" s="31" t="n">
-        <v>698673</v>
+        <v>659800</v>
       </c>
       <c r="C13" s="32" t="n">
-        <v>194</v>
-      </c>
-      <c r="D13" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E13" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>1127</v>
+      </c>
+      <c r="D13" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E13" s="34" t="n">
+        <v>0.3495281370150316</v>
       </c>
       <c r="F13" s="33" t="inlineStr">
         <is>
@@ -4835,10 +5081,10 @@
         </is>
       </c>
       <c r="H13" s="32" t="n">
-        <v>973</v>
+        <v>2000</v>
       </c>
       <c r="I13" s="34" t="n">
-        <v>0.1700454386578176</v>
+        <v>0.3495281370150316</v>
       </c>
     </row>
     <row r="14">
@@ -4848,20 +5094,16 @@
         </is>
       </c>
       <c r="B14" s="36" t="n">
-        <v>591200</v>
+        <v>522300</v>
       </c>
       <c r="C14" s="37" t="n">
-        <v>290</v>
-      </c>
-      <c r="D14" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E14" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>100</v>
+      </c>
+      <c r="D14" s="37" t="n">
+        <v>516</v>
+      </c>
+      <c r="E14" s="39" t="n">
+        <v>0.1181361954650351</v>
       </c>
       <c r="F14" s="38" t="inlineStr">
         <is>
@@ -4877,7 +5119,7 @@
         <v>516</v>
       </c>
       <c r="I14" s="39" t="n">
-        <v>0.1020198345538903</v>
+        <v>0.1181361954650351</v>
       </c>
     </row>
     <row r="15">
@@ -4887,20 +5129,16 @@
         </is>
       </c>
       <c r="B15" s="31" t="n">
-        <v>576900</v>
+        <v>486000</v>
       </c>
       <c r="C15" s="32" t="n">
-        <v>1199</v>
-      </c>
-      <c r="D15" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E15" s="33" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>11100</v>
+      </c>
+      <c r="D15" s="32" t="n">
+        <v>17775</v>
+      </c>
+      <c r="E15" s="34" t="n">
+        <v>3.960340890101932</v>
       </c>
       <c r="F15" s="33" t="inlineStr">
         <is>
@@ -4913,10 +5151,10 @@
         </is>
       </c>
       <c r="H15" s="32" t="n">
-        <v>8375</v>
+        <v>17775</v>
       </c>
       <c r="I15" s="34" t="n">
-        <v>1.523211931068968</v>
+        <v>3.960340890101932</v>
       </c>
     </row>
     <row r="16">
@@ -4926,20 +5164,16 @@
         </is>
       </c>
       <c r="B16" s="36" t="n">
-        <v>335100</v>
-      </c>
-      <c r="C16" s="42" t="n">
-        <v>-30</v>
-      </c>
-      <c r="D16" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="E16" s="38" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>335400</v>
+      </c>
+      <c r="C16" s="37" t="n">
+        <v>300</v>
+      </c>
+      <c r="D16" s="37" t="n">
+        <v>282</v>
+      </c>
+      <c r="E16" s="39" t="n">
+        <v>0.08414946377097721</v>
       </c>
       <c r="F16" s="38" t="inlineStr">
         <is>
@@ -4951,11 +5185,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="H16" s="42" t="n">
-        <v>-18</v>
-      </c>
-      <c r="I16" s="43" t="n">
-        <v>-0.005371242368357176</v>
+      <c r="H16" s="37" t="n">
+        <v>282</v>
+      </c>
+      <c r="I16" s="39" t="n">
+        <v>0.08414946377097721</v>
       </c>
     </row>
     <row r="18">
@@ -5034,10 +5268,10 @@
         <v>69000</v>
       </c>
       <c r="F22" s="46" t="n">
-        <v>84900</v>
+        <v>85000</v>
       </c>
       <c r="G22" s="47" t="n">
-        <v>591200</v>
+        <v>522300</v>
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
@@ -5047,22 +5281,22 @@
         </is>
       </c>
       <c r="B23" s="49" t="n">
-        <v>175000</v>
+        <v>183000</v>
       </c>
       <c r="C23" s="49" t="n">
-        <v>192200</v>
+        <v>192600</v>
       </c>
       <c r="D23" s="49" t="n">
-        <v>89000</v>
+        <v>91000</v>
       </c>
       <c r="E23" s="49" t="n">
         <v>102000</v>
       </c>
       <c r="F23" s="49" t="n">
-        <v>18700</v>
+        <v>19400</v>
       </c>
       <c r="G23" s="50" t="n">
-        <v>576900</v>
+        <v>486000</v>
       </c>
     </row>
     <row r="24">
@@ -5072,22 +5306,22 @@
         </is>
       </c>
       <c r="B24" s="46" t="n">
-        <v>462128</v>
+        <v>462000</v>
       </c>
       <c r="C24" s="46" t="n">
-        <v>286700</v>
+        <v>287000</v>
       </c>
       <c r="D24" s="46" t="n">
-        <v>180000</v>
+        <v>181000</v>
       </c>
       <c r="E24" s="46" t="n">
         <v>487000</v>
       </c>
       <c r="F24" s="46" t="n">
-        <v>682100</v>
+        <v>681700</v>
       </c>
       <c r="G24" s="47" t="n">
-        <v>2097928</v>
+        <v>1611700</v>
       </c>
     </row>
     <row r="25">
@@ -5097,7 +5331,7 @@
         </is>
       </c>
       <c r="B25" s="49" t="n">
-        <v>847000</v>
+        <v>867000</v>
       </c>
       <c r="C25" s="49" t="n">
         <v>2600000</v>
@@ -5112,7 +5346,7 @@
         <v>3000000</v>
       </c>
       <c r="G25" s="50" t="n">
-        <v>8385000</v>
+        <v>8367000</v>
       </c>
     </row>
     <row r="26">
@@ -5122,10 +5356,10 @@
         </is>
       </c>
       <c r="B26" s="46" t="n">
-        <v>1402635</v>
+        <v>1000000</v>
       </c>
       <c r="C26" s="46" t="n">
-        <v>626000</v>
+        <v>628800</v>
       </c>
       <c r="D26" s="46" t="n">
         <v>1200000</v>
@@ -5139,7 +5373,7 @@
         <v>2400000</v>
       </c>
       <c r="G26" s="47" t="n">
-        <v>5628635</v>
+        <v>5228800</v>
       </c>
     </row>
     <row r="27">
@@ -5149,7 +5383,7 @@
         </is>
       </c>
       <c r="B27" s="49" t="n">
-        <v>757258</v>
+        <v>758000</v>
       </c>
       <c r="C27" s="49" t="n">
         <v>3000000</v>
@@ -5166,7 +5400,7 @@
         <v>1500000</v>
       </c>
       <c r="G27" s="50" t="n">
-        <v>7357258</v>
+        <v>7358000</v>
       </c>
     </row>
     <row r="28">
@@ -5176,22 +5410,22 @@
         </is>
       </c>
       <c r="B28" s="46" t="n">
-        <v>356973</v>
+        <v>357000</v>
       </c>
       <c r="C28" s="46" t="n">
         <v>136200</v>
       </c>
       <c r="D28" s="46" t="n">
-        <v>80000</v>
+        <v>81000</v>
       </c>
       <c r="E28" s="46" t="n">
         <v>40000</v>
       </c>
       <c r="F28" s="46" t="n">
-        <v>85500</v>
+        <v>85600</v>
       </c>
       <c r="G28" s="47" t="n">
-        <v>698673</v>
+        <v>659800</v>
       </c>
     </row>
     <row r="29">
@@ -5207,7 +5441,7 @@
         <v>307800</v>
       </c>
       <c r="D29" s="49" t="n">
-        <v>180000</v>
+        <v>181000</v>
       </c>
       <c r="E29" s="49" t="n">
         <v>398000</v>
@@ -5218,7 +5452,7 @@
         </is>
       </c>
       <c r="G29" s="50" t="n">
-        <v>1124800</v>
+        <v>1125800</v>
       </c>
     </row>
     <row r="30">
@@ -5228,7 +5462,7 @@
         </is>
       </c>
       <c r="B30" s="46" t="n">
-        <v>30700</v>
+        <v>31000</v>
       </c>
       <c r="C30" s="46" t="n">
         <v>205400</v>
@@ -5245,7 +5479,7 @@
         </is>
       </c>
       <c r="G30" s="47" t="n">
-        <v>335100</v>
+        <v>335400</v>
       </c>
     </row>
     <row r="31">
@@ -5255,10 +5489,10 @@
         </is>
       </c>
       <c r="B31" s="49" t="n">
-        <v>218225</v>
+        <v>218000</v>
       </c>
       <c r="C31" s="49" t="n">
-        <v>941200</v>
+        <v>941500</v>
       </c>
       <c r="D31" s="49" t="n">
         <v>266000</v>
@@ -5272,7 +5506,7 @@
         </is>
       </c>
       <c r="G31" s="50" t="n">
-        <v>1856425</v>
+        <v>1425500</v>
       </c>
     </row>
     <row r="34" ht="20" customHeight="1">
@@ -5362,21 +5596,17 @@
       <c r="C36" s="52" t="n">
         <v>106000</v>
       </c>
-      <c r="D36" s="32" t="n">
-        <v>290</v>
-      </c>
-      <c r="E36" s="34" t="n">
-        <v>0.2743354460315928</v>
-      </c>
-      <c r="F36" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G36" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D36" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="32" t="n">
+        <v>416</v>
+      </c>
+      <c r="G36" s="34" t="n">
+        <v>0.3939990907713353</v>
       </c>
       <c r="H36" s="51" t="inlineStr">
         <is>
@@ -5415,15 +5645,11 @@
       <c r="E37" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G37" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F37" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="G37" s="34" t="n">
+        <v>0.046904315197005</v>
       </c>
       <c r="H37" s="51" t="inlineStr">
         <is>
@@ -5462,15 +5688,11 @@
       <c r="E38" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G38" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F38" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H38" s="51" t="inlineStr">
         <is>
@@ -5533,11 +5755,15 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J39" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="54" t="n">
-        <v>0</v>
+      <c r="J39" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K39" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="40">
@@ -5552,13 +5778,13 @@
         </is>
       </c>
       <c r="C40" s="52" t="n">
-        <v>84900</v>
-      </c>
-      <c r="D40" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="54" t="n">
-        <v>0</v>
+        <v>85000</v>
+      </c>
+      <c r="D40" s="32" t="n">
+        <v>100</v>
+      </c>
+      <c r="E40" s="34" t="n">
+        <v>0.1177856301531222</v>
       </c>
       <c r="F40" s="51" t="inlineStr">
         <is>
@@ -5603,23 +5829,19 @@
         </is>
       </c>
       <c r="C41" s="56" t="n">
-        <v>591200</v>
+        <v>522300</v>
       </c>
       <c r="D41" s="57" t="n">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="E41" s="58" t="n">
-        <v>0.05556513575137867</v>
-      </c>
-      <c r="F41" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G41" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.01914975105323791</v>
+      </c>
+      <c r="F41" s="57" t="n">
+        <v>516</v>
+      </c>
+      <c r="G41" s="58" t="n">
+        <v>0.1181361954650351</v>
       </c>
       <c r="H41" s="55" t="inlineStr">
         <is>
@@ -5635,7 +5857,7 @@
         <v>516</v>
       </c>
       <c r="K41" s="58" t="n">
-        <v>0.1020198345538903</v>
+        <v>0.1181361954650351</v>
       </c>
     </row>
     <row r="42">
@@ -5650,23 +5872,19 @@
         </is>
       </c>
       <c r="C42" s="52" t="n">
-        <v>175000</v>
-      </c>
-      <c r="D42" s="40" t="n">
-        <v>-101</v>
-      </c>
-      <c r="E42" s="41" t="n">
-        <v>-0.05768099553972172</v>
-      </c>
-      <c r="F42" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G42" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>183000</v>
+      </c>
+      <c r="D42" s="32" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E42" s="34" t="n">
+        <v>4.571428571428582</v>
+      </c>
+      <c r="F42" s="32" t="n">
+        <v>13975</v>
+      </c>
+      <c r="G42" s="34" t="n">
+        <v>8.268007691169954</v>
       </c>
       <c r="H42" s="51" t="inlineStr">
         <is>
@@ -5679,10 +5897,10 @@
         </is>
       </c>
       <c r="J42" s="32" t="n">
-        <v>5975</v>
+        <v>13975</v>
       </c>
       <c r="K42" s="34" t="n">
-        <v>3.534980032539559</v>
+        <v>8.268007691169954</v>
       </c>
     </row>
     <row r="43">
@@ -5697,23 +5915,19 @@
         </is>
       </c>
       <c r="C43" s="52" t="n">
-        <v>192200</v>
+        <v>192600</v>
       </c>
       <c r="D43" s="32" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="E43" s="34" t="n">
-        <v>0.05205622071837723</v>
-      </c>
-      <c r="F43" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G43" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.2081165452653577</v>
+      </c>
+      <c r="F43" s="32" t="n">
+        <v>800</v>
+      </c>
+      <c r="G43" s="34" t="n">
+        <v>0.4171011470281538</v>
       </c>
       <c r="H43" s="51" t="inlineStr">
         <is>
@@ -5726,10 +5940,10 @@
         </is>
       </c>
       <c r="J43" s="32" t="n">
-        <v>400</v>
+        <v>800</v>
       </c>
       <c r="K43" s="34" t="n">
-        <v>0.2085505735140769</v>
+        <v>0.4171011470281538</v>
       </c>
     </row>
     <row r="44">
@@ -5744,23 +5958,19 @@
         </is>
       </c>
       <c r="C44" s="52" t="n">
-        <v>89000</v>
-      </c>
-      <c r="D44" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F44" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G44" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>91000</v>
+      </c>
+      <c r="D44" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="E44" s="34" t="n">
+        <v>2.247191011235961</v>
+      </c>
+      <c r="F44" s="32" t="n">
+        <v>3000</v>
+      </c>
+      <c r="G44" s="34" t="n">
+        <v>3.409090909090917</v>
       </c>
       <c r="H44" s="51" t="inlineStr">
         <is>
@@ -5773,10 +5983,10 @@
         </is>
       </c>
       <c r="J44" s="32" t="n">
-        <v>1000</v>
+        <v>3000</v>
       </c>
       <c r="K44" s="34" t="n">
-        <v>1.136363636363646</v>
+        <v>3.409090909090917</v>
       </c>
     </row>
     <row r="45">
@@ -5793,11 +6003,15 @@
       <c r="C45" s="52" t="n">
         <v>102000</v>
       </c>
-      <c r="D45" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E45" s="34" t="n">
-        <v>0.990099009900991</v>
+      <c r="D45" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E45" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="F45" s="51" t="inlineStr">
         <is>
@@ -5819,11 +6033,15 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J45" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K45" s="34" t="n">
-        <v>0.990099009900991</v>
+      <c r="J45" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K45" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="46">
@@ -5838,13 +6056,13 @@
         </is>
       </c>
       <c r="C46" s="52" t="n">
-        <v>18700</v>
+        <v>19400</v>
       </c>
       <c r="D46" s="32" t="n">
-        <v>200</v>
+        <v>700</v>
       </c>
       <c r="E46" s="34" t="n">
-        <v>1.08108108108107</v>
+        <v>3.743315508021383</v>
       </c>
       <c r="F46" s="51" t="inlineStr">
         <is>
@@ -5889,23 +6107,19 @@
         </is>
       </c>
       <c r="C47" s="56" t="n">
-        <v>576900</v>
+        <v>486000</v>
       </c>
       <c r="D47" s="57" t="n">
-        <v>1199</v>
+        <v>11100</v>
       </c>
       <c r="E47" s="58" t="n">
-        <v>0.2082678334760502</v>
-      </c>
-      <c r="F47" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G47" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>2.337334175615924</v>
+      </c>
+      <c r="F47" s="57" t="n">
+        <v>17775</v>
+      </c>
+      <c r="G47" s="58" t="n">
+        <v>3.960340890101932</v>
       </c>
       <c r="H47" s="55" t="inlineStr">
         <is>
@@ -5918,10 +6132,10 @@
         </is>
       </c>
       <c r="J47" s="57" t="n">
-        <v>8375</v>
+        <v>17775</v>
       </c>
       <c r="K47" s="58" t="n">
-        <v>1.523211931068968</v>
+        <v>3.960340890101932</v>
       </c>
     </row>
     <row r="48">
@@ -5936,23 +6150,19 @@
         </is>
       </c>
       <c r="C48" s="52" t="n">
-        <v>462128</v>
+        <v>462000</v>
       </c>
       <c r="D48" s="40" t="n">
-        <v>-56</v>
+        <v>-128</v>
       </c>
       <c r="E48" s="41" t="n">
-        <v>-0.01211638654734504</v>
-      </c>
-      <c r="F48" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G48" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>-0.02769795381366569</v>
+      </c>
+      <c r="F48" s="32" t="n">
+        <v>218</v>
+      </c>
+      <c r="G48" s="34" t="n">
+        <v>0.04720842302212702</v>
       </c>
       <c r="H48" s="51" t="inlineStr">
         <is>
@@ -5965,10 +6175,10 @@
         </is>
       </c>
       <c r="J48" s="32" t="n">
-        <v>346</v>
+        <v>218</v>
       </c>
       <c r="K48" s="34" t="n">
-        <v>0.0749271301176746</v>
+        <v>0.04720842302212702</v>
       </c>
     </row>
     <row r="49">
@@ -5983,23 +6193,19 @@
         </is>
       </c>
       <c r="C49" s="52" t="n">
-        <v>286700</v>
-      </c>
-      <c r="D49" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F49" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G49" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>287000</v>
+      </c>
+      <c r="D49" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="E49" s="34" t="n">
+        <v>0.1046389954656446</v>
+      </c>
+      <c r="F49" s="32" t="n">
+        <v>400</v>
+      </c>
+      <c r="G49" s="34" t="n">
+        <v>0.1395673412421417</v>
       </c>
       <c r="H49" s="51" t="inlineStr">
         <is>
@@ -6012,10 +6218,10 @@
         </is>
       </c>
       <c r="J49" s="32" t="n">
-        <v>100</v>
+        <v>400</v>
       </c>
       <c r="K49" s="34" t="n">
-        <v>0.03489183531053541</v>
+        <v>0.1395673412421417</v>
       </c>
     </row>
     <row r="50">
@@ -6030,23 +6236,19 @@
         </is>
       </c>
       <c r="C50" s="52" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D50" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E50" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G50" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>181000</v>
+      </c>
+      <c r="D50" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E50" s="34" t="n">
+        <v>0.5555555555555536</v>
+      </c>
+      <c r="F50" s="32" t="n">
+        <v>5000</v>
+      </c>
+      <c r="G50" s="34" t="n">
+        <v>2.840909090909083</v>
       </c>
       <c r="H50" s="51" t="inlineStr">
         <is>
@@ -6059,10 +6261,10 @@
         </is>
       </c>
       <c r="J50" s="32" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="K50" s="34" t="n">
-        <v>2.272727272727271</v>
+        <v>2.840909090909083</v>
       </c>
     </row>
     <row r="51">
@@ -6109,11 +6311,15 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J51" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="54" t="n">
-        <v>0</v>
+      <c r="J51" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K51" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="52">
@@ -6128,13 +6334,13 @@
         </is>
       </c>
       <c r="C52" s="52" t="n">
-        <v>682100</v>
-      </c>
-      <c r="D52" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="54" t="n">
-        <v>0</v>
+        <v>681700</v>
+      </c>
+      <c r="D52" s="40" t="n">
+        <v>-400</v>
+      </c>
+      <c r="E52" s="41" t="n">
+        <v>-0.05864242779650697</v>
       </c>
       <c r="F52" s="51" t="inlineStr">
         <is>
@@ -6179,23 +6385,19 @@
         </is>
       </c>
       <c r="C53" s="56" t="n">
-        <v>2097928</v>
-      </c>
-      <c r="D53" s="59" t="n">
-        <v>-56</v>
-      </c>
-      <c r="E53" s="60" t="n">
-        <v>-0.003476136324132018</v>
-      </c>
-      <c r="F53" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G53" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>1611700</v>
+      </c>
+      <c r="D53" s="57" t="n">
+        <v>772</v>
+      </c>
+      <c r="E53" s="58" t="n">
+        <v>0.04792268804068023</v>
+      </c>
+      <c r="F53" s="57" t="n">
+        <v>5618</v>
+      </c>
+      <c r="G53" s="58" t="n">
+        <v>0.6077573989973883</v>
       </c>
       <c r="H53" s="55" t="inlineStr">
         <is>
@@ -6208,10 +6410,10 @@
         </is>
       </c>
       <c r="J53" s="57" t="n">
-        <v>4446</v>
+        <v>5618</v>
       </c>
       <c r="K53" s="58" t="n">
-        <v>0.3150103940676496</v>
+        <v>0.6077573989973883</v>
       </c>
     </row>
     <row r="54">
@@ -6226,23 +6428,19 @@
         </is>
       </c>
       <c r="C54" s="52" t="n">
-        <v>847000</v>
-      </c>
-      <c r="D54" s="40" t="n">
-        <v>-736</v>
-      </c>
-      <c r="E54" s="41" t="n">
-        <v>-0.08681948153670405</v>
-      </c>
-      <c r="F54" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G54" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>867000</v>
+      </c>
+      <c r="D54" s="32" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E54" s="34" t="n">
+        <v>2.361275088547821</v>
+      </c>
+      <c r="F54" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="G54" s="34" t="n">
+        <v>3.443215401704491</v>
       </c>
       <c r="H54" s="51" t="inlineStr">
         <is>
@@ -6255,10 +6453,10 @@
         </is>
       </c>
       <c r="J54" s="32" t="n">
-        <v>8859</v>
+        <v>28859</v>
       </c>
       <c r="K54" s="34" t="n">
-        <v>1.056982059104605</v>
+        <v>3.443215401704491</v>
       </c>
     </row>
     <row r="55">
@@ -6281,15 +6479,11 @@
       <c r="E55" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G55" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F55" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H55" s="51" t="inlineStr">
         <is>
@@ -6328,15 +6522,11 @@
       <c r="E56" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G56" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F56" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H56" s="51" t="inlineStr">
         <is>
@@ -6473,23 +6663,19 @@
         </is>
       </c>
       <c r="C59" s="56" t="n">
-        <v>8385000</v>
-      </c>
-      <c r="D59" s="59" t="n">
-        <v>-736</v>
-      </c>
-      <c r="E59" s="60" t="n">
-        <v>-0.008816761814223195</v>
-      </c>
-      <c r="F59" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G59" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>8367000</v>
+      </c>
+      <c r="D59" s="57" t="n">
+        <v>20000</v>
+      </c>
+      <c r="E59" s="58" t="n">
+        <v>0.2396070444470988</v>
+      </c>
+      <c r="F59" s="57" t="n">
+        <v>28859</v>
+      </c>
+      <c r="G59" s="58" t="n">
+        <v>0.5406189158360553</v>
       </c>
       <c r="H59" s="55" t="inlineStr">
         <is>
@@ -6502,10 +6688,10 @@
         </is>
       </c>
       <c r="J59" s="57" t="n">
-        <v>8859</v>
+        <v>28859</v>
       </c>
       <c r="K59" s="58" t="n">
-        <v>0.165956650451915</v>
+        <v>0.5406189158360553</v>
       </c>
     </row>
     <row r="60">
@@ -6520,23 +6706,19 @@
         </is>
       </c>
       <c r="C60" s="52" t="n">
-        <v>1402635</v>
-      </c>
-      <c r="D60" s="32" t="n">
-        <v>69</v>
-      </c>
-      <c r="E60" s="34" t="n">
-        <v>0.004919554587812236</v>
-      </c>
-      <c r="F60" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G60" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>1000000</v>
+      </c>
+      <c r="D60" s="40" t="n">
+        <v>-402635</v>
+      </c>
+      <c r="E60" s="41" t="n">
+        <v>-28.70561478930727</v>
+      </c>
+      <c r="F60" s="40" t="n">
+        <v>-402767</v>
+      </c>
+      <c r="G60" s="41" t="n">
+        <v>-28.7123235719118</v>
       </c>
       <c r="H60" s="51" t="inlineStr">
         <is>
@@ -6549,10 +6731,10 @@
         </is>
       </c>
       <c r="J60" s="40" t="n">
-        <v>-132</v>
+        <v>-402767</v>
       </c>
       <c r="K60" s="41" t="n">
-        <v>-0.00940997328851001</v>
+        <v>-28.7123235719118</v>
       </c>
     </row>
     <row r="61">
@@ -6567,23 +6749,19 @@
         </is>
       </c>
       <c r="C61" s="52" t="n">
-        <v>626000</v>
+        <v>628800</v>
       </c>
       <c r="D61" s="32" t="n">
-        <v>100</v>
+        <v>2800</v>
       </c>
       <c r="E61" s="34" t="n">
-        <v>0.01597699312989587</v>
-      </c>
-      <c r="F61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G61" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.4472843450479269</v>
+      </c>
+      <c r="F61" s="32" t="n">
+        <v>3100</v>
+      </c>
+      <c r="G61" s="34" t="n">
+        <v>0.4954451014863359</v>
       </c>
       <c r="H61" s="51" t="inlineStr">
         <is>
@@ -6596,10 +6774,10 @@
         </is>
       </c>
       <c r="J61" s="32" t="n">
-        <v>300</v>
+        <v>3100</v>
       </c>
       <c r="K61" s="34" t="n">
-        <v>0.04794630014384182</v>
+        <v>0.4954451014863359</v>
       </c>
     </row>
     <row r="62">
@@ -6622,15 +6800,11 @@
       <c r="E62" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G62" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F62" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H62" s="51" t="inlineStr">
         <is>
@@ -6712,23 +6886,19 @@
         </is>
       </c>
       <c r="C64" s="56" t="n">
-        <v>5628635</v>
-      </c>
-      <c r="D64" s="57" t="n">
-        <v>169</v>
-      </c>
-      <c r="E64" s="58" t="n">
-        <v>0.003002594312562223</v>
-      </c>
-      <c r="F64" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G64" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>5228800</v>
+      </c>
+      <c r="D64" s="59" t="n">
+        <v>-399835</v>
+      </c>
+      <c r="E64" s="60" t="n">
+        <v>-7.103587281818768</v>
+      </c>
+      <c r="F64" s="59" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="G64" s="60" t="n">
+        <v>-12.37946678717794</v>
       </c>
       <c r="H64" s="55" t="inlineStr">
         <is>
@@ -6740,11 +6910,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J64" s="57" t="n">
-        <v>168</v>
-      </c>
-      <c r="K64" s="58" t="n">
-        <v>0.005203708137635488</v>
+      <c r="J64" s="59" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="K64" s="60" t="n">
+        <v>-12.37946678717794</v>
       </c>
     </row>
     <row r="65">
@@ -6759,23 +6929,19 @@
         </is>
       </c>
       <c r="C65" s="52" t="n">
-        <v>757258</v>
+        <v>758000</v>
       </c>
       <c r="D65" s="32" t="n">
-        <v>155</v>
+        <v>742</v>
       </c>
       <c r="E65" s="34" t="n">
-        <v>0.02047277583103746</v>
-      </c>
-      <c r="F65" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G65" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.09798509886986828</v>
+      </c>
+      <c r="F65" s="32" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G65" s="34" t="n">
+        <v>0.1604152296686312</v>
       </c>
       <c r="H65" s="51" t="inlineStr">
         <is>
@@ -6788,10 +6954,10 @@
         </is>
       </c>
       <c r="J65" s="32" t="n">
-        <v>472</v>
+        <v>1214</v>
       </c>
       <c r="K65" s="34" t="n">
-        <v>0.06236901845435572</v>
+        <v>0.1604152296686312</v>
       </c>
     </row>
     <row r="66">
@@ -6814,15 +6980,11 @@
       <c r="E66" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G66" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F66" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H66" s="51" t="inlineStr">
         <is>
@@ -6861,15 +7023,11 @@
       <c r="E67" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G67" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F67" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H67" s="51" t="inlineStr">
         <is>
@@ -6951,23 +7109,19 @@
         </is>
       </c>
       <c r="C69" s="56" t="n">
-        <v>7357258</v>
+        <v>7358000</v>
       </c>
       <c r="D69" s="57" t="n">
-        <v>155</v>
+        <v>742</v>
       </c>
       <c r="E69" s="58" t="n">
-        <v>0.002106807530077859</v>
-      </c>
-      <c r="F69" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G69" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.01008527905368428</v>
+      </c>
+      <c r="F69" s="57" t="n">
+        <v>1214</v>
+      </c>
+      <c r="G69" s="58" t="n">
+        <v>0.02072809216522309</v>
       </c>
       <c r="H69" s="55" t="inlineStr">
         <is>
@@ -6980,10 +7134,10 @@
         </is>
       </c>
       <c r="J69" s="57" t="n">
-        <v>472</v>
+        <v>1214</v>
       </c>
       <c r="K69" s="58" t="n">
-        <v>0.008059027596374335</v>
+        <v>0.02072809216522309</v>
       </c>
     </row>
     <row r="70">
@@ -6998,23 +7152,19 @@
         </is>
       </c>
       <c r="C70" s="52" t="n">
-        <v>356973</v>
+        <v>357000</v>
       </c>
       <c r="D70" s="32" t="n">
-        <v>94</v>
+        <v>27</v>
       </c>
       <c r="E70" s="34" t="n">
-        <v>0.02633945959273909</v>
-      </c>
-      <c r="F70" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G70" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.007563597246851295</v>
+      </c>
+      <c r="F70" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G70" s="34" t="n">
+        <v>0.2808988764045006</v>
       </c>
       <c r="H70" s="51" t="inlineStr">
         <is>
@@ -7027,10 +7177,10 @@
         </is>
       </c>
       <c r="J70" s="32" t="n">
-        <v>973</v>
+        <v>1000</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>0.2733146067415815</v>
+        <v>0.2808988764045006</v>
       </c>
     </row>
     <row r="71">
@@ -7053,15 +7203,11 @@
       <c r="E71" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G71" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F71" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H71" s="51" t="inlineStr">
         <is>
@@ -7092,23 +7238,19 @@
         </is>
       </c>
       <c r="C72" s="52" t="n">
-        <v>80000</v>
-      </c>
-      <c r="D72" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E72" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G72" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>81000</v>
+      </c>
+      <c r="D72" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E72" s="34" t="n">
+        <v>1.249999999999996</v>
+      </c>
+      <c r="F72" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G72" s="34" t="n">
+        <v>1.249999999999996</v>
       </c>
       <c r="H72" s="51" t="inlineStr">
         <is>
@@ -7120,11 +7262,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J72" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K72" s="54" t="n">
-        <v>0</v>
+      <c r="J72" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K72" s="34" t="n">
+        <v>1.249999999999996</v>
       </c>
     </row>
     <row r="73">
@@ -7194,13 +7336,13 @@
         </is>
       </c>
       <c r="C74" s="52" t="n">
-        <v>85500</v>
+        <v>85600</v>
       </c>
       <c r="D74" s="32" t="n">
         <v>100</v>
       </c>
       <c r="E74" s="34" t="n">
-        <v>0.117096018735352</v>
+        <v>0.1169590643274931</v>
       </c>
       <c r="F74" s="51" t="inlineStr">
         <is>
@@ -7245,23 +7387,19 @@
         </is>
       </c>
       <c r="C75" s="56" t="n">
-        <v>698673</v>
+        <v>659800</v>
       </c>
       <c r="D75" s="57" t="n">
-        <v>194</v>
+        <v>1127</v>
       </c>
       <c r="E75" s="58" t="n">
-        <v>0.02946183553309556</v>
-      </c>
-      <c r="F75" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G75" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.1711015936587623</v>
+      </c>
+      <c r="F75" s="57" t="n">
+        <v>2000</v>
+      </c>
+      <c r="G75" s="58" t="n">
+        <v>0.3495281370150316</v>
       </c>
       <c r="H75" s="55" t="inlineStr">
         <is>
@@ -7274,10 +7412,10 @@
         </is>
       </c>
       <c r="J75" s="57" t="n">
-        <v>973</v>
+        <v>2000</v>
       </c>
       <c r="K75" s="58" t="n">
-        <v>0.1700454386578176</v>
+        <v>0.3495281370150316</v>
       </c>
     </row>
     <row r="76">
@@ -7294,21 +7432,17 @@
       <c r="C76" s="52" t="n">
         <v>637000</v>
       </c>
-      <c r="D76" s="32" t="n">
-        <v>117</v>
-      </c>
-      <c r="E76" s="34" t="n">
-        <v>0.01837072115287164</v>
-      </c>
-      <c r="F76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G76" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="D76" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="E76" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="32" t="n">
+        <v>482</v>
+      </c>
+      <c r="G76" s="34" t="n">
+        <v>0.07572448854549219</v>
       </c>
       <c r="H76" s="51" t="inlineStr">
         <is>
@@ -7347,15 +7481,11 @@
       <c r="E77" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G77" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F77" s="40" t="n">
+        <v>-100</v>
+      </c>
+      <c r="G77" s="41" t="n">
+        <v>-0.03247807729782615</v>
       </c>
       <c r="H77" s="51" t="inlineStr">
         <is>
@@ -7386,23 +7516,19 @@
         </is>
       </c>
       <c r="C78" s="52" t="n">
-        <v>180000</v>
-      </c>
-      <c r="D78" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E78" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G78" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>181000</v>
+      </c>
+      <c r="D78" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E78" s="34" t="n">
+        <v>0.5555555555555536</v>
+      </c>
+      <c r="F78" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="G78" s="34" t="n">
+        <v>0.5555555555555536</v>
       </c>
       <c r="H78" s="51" t="inlineStr">
         <is>
@@ -7414,11 +7540,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J78" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K78" s="54" t="n">
-        <v>0</v>
+      <c r="J78" s="32" t="n">
+        <v>1000</v>
+      </c>
+      <c r="K78" s="34" t="n">
+        <v>0.5555555555555536</v>
       </c>
     </row>
     <row r="79">
@@ -7488,23 +7614,19 @@
         </is>
       </c>
       <c r="C80" s="56" t="n">
-        <v>1124800</v>
+        <v>1125800</v>
       </c>
       <c r="D80" s="57" t="n">
-        <v>117</v>
+        <v>1000</v>
       </c>
       <c r="E80" s="58" t="n">
-        <v>0.01040293131486791</v>
-      </c>
-      <c r="F80" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G80" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.08890469416784619</v>
+      </c>
+      <c r="F80" s="57" t="n">
+        <v>1382</v>
+      </c>
+      <c r="G80" s="58" t="n">
+        <v>0.1229080288647211</v>
       </c>
       <c r="H80" s="55" t="inlineStr">
         <is>
@@ -7517,10 +7639,10 @@
         </is>
       </c>
       <c r="J80" s="57" t="n">
-        <v>382</v>
+        <v>1382</v>
       </c>
       <c r="K80" s="58" t="n">
-        <v>0.03397313098865151</v>
+        <v>0.1229080288647211</v>
       </c>
     </row>
     <row r="81">
@@ -7535,23 +7657,19 @@
         </is>
       </c>
       <c r="C81" s="52" t="n">
-        <v>30700</v>
-      </c>
-      <c r="D81" s="40" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E81" s="41" t="n">
-        <v>-0.09762447120078566</v>
-      </c>
-      <c r="F81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G81" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>31000</v>
+      </c>
+      <c r="D81" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="E81" s="34" t="n">
+        <v>0.9771986970684043</v>
+      </c>
+      <c r="F81" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="G81" s="34" t="n">
+        <v>0.9180285174816172</v>
       </c>
       <c r="H81" s="51" t="inlineStr">
         <is>
@@ -7563,11 +7681,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J81" s="40" t="n">
-        <v>-18</v>
-      </c>
-      <c r="K81" s="41" t="n">
-        <v>-0.05859756494563939</v>
+      <c r="J81" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="K81" s="34" t="n">
+        <v>0.9180285174816172</v>
       </c>
     </row>
     <row r="82">
@@ -7590,15 +7708,11 @@
       <c r="E82" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G82" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F82" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G82" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H82" s="51" t="inlineStr">
         <is>
@@ -7637,15 +7751,11 @@
       <c r="E83" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G83" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F83" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G83" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H83" s="51" t="inlineStr">
         <is>
@@ -7731,23 +7841,19 @@
         </is>
       </c>
       <c r="C85" s="56" t="n">
-        <v>335100</v>
-      </c>
-      <c r="D85" s="59" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E85" s="60" t="n">
-        <v>-0.008951750067143216</v>
-      </c>
-      <c r="F85" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G85" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>335400</v>
+      </c>
+      <c r="D85" s="57" t="n">
+        <v>300</v>
+      </c>
+      <c r="E85" s="58" t="n">
+        <v>0.08952551477170445</v>
+      </c>
+      <c r="F85" s="57" t="n">
+        <v>282</v>
+      </c>
+      <c r="G85" s="58" t="n">
+        <v>0.08414946377097721</v>
       </c>
       <c r="H85" s="55" t="inlineStr">
         <is>
@@ -7759,11 +7865,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J85" s="59" t="n">
-        <v>-18</v>
-      </c>
-      <c r="K85" s="60" t="n">
-        <v>-0.005371242368357176</v>
+      <c r="J85" s="57" t="n">
+        <v>282</v>
+      </c>
+      <c r="K85" s="58" t="n">
+        <v>0.08414946377097721</v>
       </c>
     </row>
     <row r="86" ht="20" customHeight="1">
@@ -7778,23 +7884,19 @@
         </is>
       </c>
       <c r="C86" s="52" t="n">
-        <v>218225</v>
-      </c>
-      <c r="D86" s="32" t="n">
-        <v>93</v>
-      </c>
-      <c r="E86" s="34" t="n">
-        <v>0.04263473493113512</v>
-      </c>
-      <c r="F86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G86" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>218000</v>
+      </c>
+      <c r="D86" s="40" t="n">
+        <v>-225</v>
+      </c>
+      <c r="E86" s="41" t="n">
+        <v>-0.1031045938824637</v>
+      </c>
+      <c r="F86" s="32" t="n">
+        <v>149</v>
+      </c>
+      <c r="G86" s="34" t="n">
+        <v>0.06839537114817773</v>
       </c>
       <c r="H86" s="51" t="inlineStr">
         <is>
@@ -7807,10 +7909,10 @@
         </is>
       </c>
       <c r="J86" s="32" t="n">
-        <v>374</v>
+        <v>149</v>
       </c>
       <c r="K86" s="34" t="n">
-        <v>0.1716769718752786</v>
+        <v>0.06839537114817773</v>
       </c>
     </row>
     <row r="87" ht="30" customHeight="1">
@@ -7825,23 +7927,19 @@
         </is>
       </c>
       <c r="C87" s="52" t="n">
-        <v>941200</v>
-      </c>
-      <c r="D87" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E87" s="54" t="n">
-        <v>0</v>
-      </c>
-      <c r="F87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G87" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>941500</v>
+      </c>
+      <c r="D87" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="E87" s="34" t="n">
+        <v>0.03187420314492151</v>
+      </c>
+      <c r="F87" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="G87" s="34" t="n">
+        <v>0.03187420314492151</v>
       </c>
       <c r="H87" s="51" t="inlineStr">
         <is>
@@ -7853,11 +7951,11 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J87" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="K87" s="54" t="n">
-        <v>0</v>
+      <c r="J87" s="32" t="n">
+        <v>300</v>
+      </c>
+      <c r="K87" s="34" t="n">
+        <v>0.03187420314492151</v>
       </c>
     </row>
     <row r="88" ht="20" customHeight="1">
@@ -7880,15 +7978,11 @@
       <c r="E88" s="54" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G88" s="51" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+      <c r="F88" s="53" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" s="54" t="n">
+        <v>0</v>
       </c>
       <c r="H88" s="51" t="inlineStr">
         <is>
@@ -7921,11 +8015,15 @@
       <c r="C89" s="52" t="n">
         <v>431000</v>
       </c>
-      <c r="D89" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="E89" s="54" t="n">
-        <v>0</v>
+      <c r="D89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="E89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
       <c r="F89" s="51" t="inlineStr">
         <is>
@@ -7947,11 +8045,15 @@
           <t>NA</t>
         </is>
       </c>
-      <c r="J89" s="32" t="n">
-        <v>1000</v>
-      </c>
-      <c r="K89" s="34" t="n">
-        <v>0.2325581395348886</v>
+      <c r="J89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="K89" s="51" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
       </c>
     </row>
     <row r="90" ht="20" customHeight="1">
@@ -7966,23 +8068,19 @@
         </is>
       </c>
       <c r="C90" s="56" t="n">
-        <v>1856425</v>
+        <v>1425500</v>
       </c>
       <c r="D90" s="57" t="n">
-        <v>93</v>
+        <v>75</v>
       </c>
       <c r="E90" s="58" t="n">
-        <v>0.005009879698247843</v>
-      </c>
-      <c r="F90" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="G90" s="55" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
+        <v>0.005261588648997062</v>
+      </c>
+      <c r="F90" s="57" t="n">
+        <v>449</v>
+      </c>
+      <c r="G90" s="58" t="n">
+        <v>0.03150764428780928</v>
       </c>
       <c r="H90" s="55" t="inlineStr">
         <is>
@@ -7995,10 +8093,10 @@
         </is>
       </c>
       <c r="J90" s="57" t="n">
-        <v>1374</v>
+        <v>449</v>
       </c>
       <c r="K90" s="58" t="n">
-        <v>0.07406804449041626</v>
+        <v>0.03150764428780928</v>
       </c>
     </row>
     <row r="91" ht="20" customHeight="1"/>
@@ -8055,391 +8153,1228 @@
       </c>
     </row>
     <row r="95" ht="20" customHeight="1">
-      <c r="A95" s="13" t="inlineStr">
+      <c r="A95" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B95" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C95" s="34" t="n">
+        <v>3.960340890101932</v>
+      </c>
+      <c r="D95" s="32" t="n">
+        <v>17775</v>
+      </c>
+      <c r="F95" s="45" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="G95" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="H95" s="34" t="n">
+        <v>0.5406189158360553</v>
+      </c>
+    </row>
+    <row r="96" ht="30" customHeight="1">
+      <c r="A96" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B96" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C96" s="34" t="n">
+        <v>0.6077573989973883</v>
+      </c>
+      <c r="D96" s="32" t="n">
+        <v>5618</v>
+      </c>
+      <c r="F96" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="G96" s="32" t="n">
+        <v>17775</v>
+      </c>
+      <c r="H96" s="34" t="n">
+        <v>3.960340890101932</v>
+      </c>
+    </row>
+    <row r="97" ht="20" customHeight="1">
+      <c r="A97" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B97" s="45" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C97" s="34" t="n">
+        <v>0.5406189158360553</v>
+      </c>
+      <c r="D97" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="F97" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="G97" s="32" t="n">
+        <v>5618</v>
+      </c>
+      <c r="H97" s="34" t="n">
+        <v>0.6077573989973883</v>
+      </c>
+    </row>
+    <row r="98" ht="30" customHeight="1">
+      <c r="A98" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B98" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C98" s="34" t="n">
+        <v>0.3495281370150316</v>
+      </c>
+      <c r="D98" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F98" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="G98" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H98" s="34" t="n">
+        <v>0.3495281370150316</v>
+      </c>
+    </row>
+    <row r="99" ht="20" customHeight="1">
+      <c r="A99" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B99" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C99" s="34" t="n">
+        <v>0.1229080288647211</v>
+      </c>
+      <c r="D99" s="32" t="n">
+        <v>1382</v>
+      </c>
+      <c r="F99" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="G99" s="32" t="n">
+        <v>1382</v>
+      </c>
+      <c r="H99" s="34" t="n">
+        <v>0.1229080288647211</v>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B100" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C100" s="34" t="n">
+        <v>0.1181361954650351</v>
+      </c>
+      <c r="D100" s="32" t="n">
+        <v>516</v>
+      </c>
+      <c r="F100" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="G100" s="32" t="n">
+        <v>1214</v>
+      </c>
+      <c r="H100" s="34" t="n">
+        <v>0.02072809216522309</v>
+      </c>
+    </row>
+    <row r="101" ht="20" customHeight="1">
+      <c r="A101" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B101" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C101" s="34" t="n">
+        <v>0.08414946377097721</v>
+      </c>
+      <c r="D101" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="F101" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="G101" s="32" t="n">
+        <v>516</v>
+      </c>
+      <c r="H101" s="34" t="n">
+        <v>0.1181361954650351</v>
+      </c>
+    </row>
+    <row r="102" ht="30" customHeight="1">
+      <c r="A102" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B102" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C102" s="34" t="n">
+        <v>0.03150764428780928</v>
+      </c>
+      <c r="D102" s="32" t="n">
+        <v>449</v>
+      </c>
+      <c r="F102" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="G102" s="32" t="n">
+        <v>449</v>
+      </c>
+      <c r="H102" s="34" t="n">
+        <v>0.03150764428780928</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B103" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C103" s="34" t="n">
+        <v>0.02072809216522309</v>
+      </c>
+      <c r="D103" s="32" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F103" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="G103" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="H103" s="34" t="n">
+        <v>0.08414946377097721</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B104" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C104" s="41" t="n">
+        <v>-12.37946678717794</v>
+      </c>
+      <c r="D104" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="F104" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="G104" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="H104" s="41" t="n">
+        <v>-12.37946678717794</v>
+      </c>
+    </row>
+    <row r="107" ht="20" customHeight="1">
+      <c r="A107" s="27" t="inlineStr">
+        <is>
+          <t>CLASSEMENT CROISSANCE 30 JOURS</t>
+        </is>
+      </c>
+      <c r="B107" s="28" t="n"/>
+      <c r="C107" s="28" t="n"/>
+      <c r="D107" s="28" t="n"/>
+      <c r="E107" s="28" t="n"/>
+      <c r="F107" s="28" t="n"/>
+      <c r="G107" s="28" t="n"/>
+    </row>
+    <row r="108" ht="30" customHeight="1">
+      <c r="A108" s="29" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B108" s="29" t="inlineStr">
+        <is>
+          <t>Par CROISSANCE %</t>
+        </is>
+      </c>
+      <c r="C108" s="29" t="inlineStr">
+        <is>
+          <t>Croissance %</t>
+        </is>
+      </c>
+      <c r="D108" s="29" t="inlineStr">
+        <is>
+          <t>Gain abonnes</t>
+        </is>
+      </c>
+      <c r="E108" s="29" t="inlineStr"/>
+      <c r="F108" s="29" t="inlineStr">
+        <is>
+          <t>Par GAIN d'abonnes</t>
+        </is>
+      </c>
+      <c r="G108" s="29" t="inlineStr">
+        <is>
+          <t>Gain abonnes</t>
+        </is>
+      </c>
+      <c r="H108" s="29" t="inlineStr">
+        <is>
+          <t>Croissance %</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="13" t="inlineStr">
         <is>
           <t>Pas encore assez d'historique pour cette periode.</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="30" customHeight="1"/>
-    <row r="97" ht="20" customHeight="1">
-      <c r="A97" s="27" t="inlineStr">
-        <is>
-          <t>CLASSEMENT CROISSANCE 30 JOURS</t>
-        </is>
-      </c>
-      <c r="B97" s="28" t="n"/>
-      <c r="C97" s="28" t="n"/>
-      <c r="D97" s="28" t="n"/>
-      <c r="E97" s="28" t="n"/>
-      <c r="F97" s="28" t="n"/>
-      <c r="G97" s="28" t="n"/>
-    </row>
-    <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="29" t="inlineStr">
+    <row r="111" ht="20" customHeight="1">
+      <c r="A111" s="27" t="inlineStr">
+        <is>
+          <t>CLASSEMENT CROISSANCE DEPUIS LE DEBUT DU SUIVI</t>
+        </is>
+      </c>
+      <c r="B111" s="28" t="n"/>
+      <c r="C111" s="28" t="n"/>
+      <c r="D111" s="28" t="n"/>
+      <c r="E111" s="28" t="n"/>
+      <c r="F111" s="28" t="n"/>
+      <c r="G111" s="28" t="n"/>
+    </row>
+    <row r="112" ht="30" customHeight="1">
+      <c r="A112" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B98" s="29" t="inlineStr">
+      <c r="B112" s="29" t="inlineStr">
         <is>
           <t>Par CROISSANCE %</t>
         </is>
       </c>
-      <c r="C98" s="29" t="inlineStr">
+      <c r="C112" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D98" s="29" t="inlineStr">
+      <c r="D112" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E98" s="29" t="inlineStr"/>
-      <c r="F98" s="29" t="inlineStr">
+      <c r="E112" s="29" t="inlineStr"/>
+      <c r="F112" s="29" t="inlineStr">
         <is>
           <t>Par GAIN d'abonnes</t>
         </is>
       </c>
-      <c r="G98" s="29" t="inlineStr">
+      <c r="G112" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H98" s="29" t="inlineStr">
+      <c r="H112" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="20" customHeight="1">
-      <c r="A99" s="13" t="inlineStr">
-        <is>
-          <t>Pas encore assez d'historique pour cette periode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" ht="30" customHeight="1"/>
-    <row r="101" ht="20" customHeight="1">
-      <c r="A101" s="27" t="inlineStr">
-        <is>
-          <t>CLASSEMENT CROISSANCE DEPUIS LE DEBUT DU SUIVI</t>
-        </is>
-      </c>
-      <c r="B101" s="28" t="n"/>
-      <c r="C101" s="28" t="n"/>
-      <c r="D101" s="28" t="n"/>
-      <c r="E101" s="28" t="n"/>
-      <c r="F101" s="28" t="n"/>
-      <c r="G101" s="28" t="n"/>
-    </row>
-    <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="29" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B113" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C113" s="34" t="n">
+        <v>3.960340890101932</v>
+      </c>
+      <c r="D113" s="32" t="n">
+        <v>17775</v>
+      </c>
+      <c r="F113" s="45" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="G113" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="H113" s="34" t="n">
+        <v>0.5406189158360553</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B114" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C114" s="34" t="n">
+        <v>0.6077573989973883</v>
+      </c>
+      <c r="D114" s="32" t="n">
+        <v>5618</v>
+      </c>
+      <c r="F114" s="45" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="G114" s="32" t="n">
+        <v>17775</v>
+      </c>
+      <c r="H114" s="34" t="n">
+        <v>3.960340890101932</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B115" s="45" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C115" s="34" t="n">
+        <v>0.5406189158360553</v>
+      </c>
+      <c r="D115" s="32" t="n">
+        <v>28859</v>
+      </c>
+      <c r="F115" s="45" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="G115" s="32" t="n">
+        <v>5618</v>
+      </c>
+      <c r="H115" s="34" t="n">
+        <v>0.6077573989973883</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B116" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C116" s="34" t="n">
+        <v>0.3495281370150316</v>
+      </c>
+      <c r="D116" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="F116" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="G116" s="32" t="n">
+        <v>2000</v>
+      </c>
+      <c r="H116" s="34" t="n">
+        <v>0.3495281370150316</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B117" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C117" s="34" t="n">
+        <v>0.1229080288647211</v>
+      </c>
+      <c r="D117" s="32" t="n">
+        <v>1382</v>
+      </c>
+      <c r="F117" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="G117" s="32" t="n">
+        <v>1382</v>
+      </c>
+      <c r="H117" s="34" t="n">
+        <v>0.1229080288647211</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B118" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C118" s="34" t="n">
+        <v>0.1181361954650351</v>
+      </c>
+      <c r="D118" s="32" t="n">
+        <v>516</v>
+      </c>
+      <c r="F118" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="G118" s="32" t="n">
+        <v>1214</v>
+      </c>
+      <c r="H118" s="34" t="n">
+        <v>0.02072809216522309</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B119" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C119" s="34" t="n">
+        <v>0.08414946377097721</v>
+      </c>
+      <c r="D119" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="F119" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="G119" s="32" t="n">
+        <v>516</v>
+      </c>
+      <c r="H119" s="34" t="n">
+        <v>0.1181361954650351</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B120" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C120" s="34" t="n">
+        <v>0.03150764428780928</v>
+      </c>
+      <c r="D120" s="32" t="n">
+        <v>449</v>
+      </c>
+      <c r="F120" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="G120" s="32" t="n">
+        <v>449</v>
+      </c>
+      <c r="H120" s="34" t="n">
+        <v>0.03150764428780928</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B121" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C121" s="34" t="n">
+        <v>0.02072809216522309</v>
+      </c>
+      <c r="D121" s="32" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F121" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="G121" s="32" t="n">
+        <v>282</v>
+      </c>
+      <c r="H121" s="34" t="n">
+        <v>0.08414946377097721</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B122" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C122" s="41" t="n">
+        <v>-12.37946678717794</v>
+      </c>
+      <c r="D122" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="F122" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="G122" s="40" t="n">
+        <v>-399667</v>
+      </c>
+      <c r="H122" s="41" t="n">
+        <v>-12.37946678717794</v>
+      </c>
+    </row>
+    <row r="125" ht="20" customHeight="1">
+      <c r="A125" s="27" t="inlineStr">
+        <is>
+          <t>INSTAGRAM - 7 JOURS</t>
+        </is>
+      </c>
+      <c r="B125" s="28" t="n"/>
+      <c r="C125" s="28" t="n"/>
+      <c r="D125" s="28" t="n"/>
+    </row>
+    <row r="126" ht="30" customHeight="1">
+      <c r="A126" s="29" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B102" s="29" t="inlineStr">
-        <is>
-          <t>Par CROISSANCE %</t>
-        </is>
-      </c>
-      <c r="C102" s="29" t="inlineStr">
+      <c r="B126" s="29" t="inlineStr">
+        <is>
+          <t>PERSONNE</t>
+        </is>
+      </c>
+      <c r="C126" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-      <c r="D102" s="29" t="inlineStr">
+      <c r="D126" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="E102" s="29" t="inlineStr"/>
-      <c r="F102" s="29" t="inlineStr">
-        <is>
-          <t>Par GAIN d'abonnes</t>
-        </is>
-      </c>
-      <c r="G102" s="29" t="inlineStr">
+    </row>
+    <row r="127">
+      <c r="A127" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B127" s="63" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C127" s="34" t="n">
+        <v>8.268007691169954</v>
+      </c>
+      <c r="D127" s="32" t="n">
+        <v>13975</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B128" s="63" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C128" s="34" t="n">
+        <v>3.443215401704491</v>
+      </c>
+      <c r="D128" s="32" t="n">
+        <v>28859</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B129" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C129" s="34" t="n">
+        <v>0.9180285174816172</v>
+      </c>
+      <c r="D129" s="32" t="n">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B130" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C130" s="34" t="n">
+        <v>0.3939990907713353</v>
+      </c>
+      <c r="D130" s="32" t="n">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B131" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C131" s="34" t="n">
+        <v>0.2808988764045006</v>
+      </c>
+      <c r="D131" s="32" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B132" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C132" s="34" t="n">
+        <v>0.1604152296686312</v>
+      </c>
+      <c r="D132" s="32" t="n">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B133" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C133" s="34" t="n">
+        <v>0.07572448854549219</v>
+      </c>
+      <c r="D133" s="32" t="n">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B134" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C134" s="34" t="n">
+        <v>0.06839537114817773</v>
+      </c>
+      <c r="D134" s="32" t="n">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B135" s="63" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C135" s="34" t="n">
+        <v>0.04720842302212702</v>
+      </c>
+      <c r="D135" s="32" t="n">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B136" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C136" s="41" t="n">
+        <v>-28.7123235719118</v>
+      </c>
+      <c r="D136" s="40" t="n">
+        <v>-402767</v>
+      </c>
+    </row>
+    <row r="138" ht="20" customHeight="1">
+      <c r="A138" s="27" t="inlineStr">
+        <is>
+          <t>X - 7 JOURS</t>
+        </is>
+      </c>
+      <c r="B138" s="28" t="n"/>
+      <c r="C138" s="28" t="n"/>
+      <c r="D138" s="28" t="n"/>
+    </row>
+    <row r="139" ht="30" customHeight="1">
+      <c r="A139" s="29" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B139" s="29" t="inlineStr">
+        <is>
+          <t>PERSONNE</t>
+        </is>
+      </c>
+      <c r="C139" s="29" t="inlineStr">
+        <is>
+          <t>Croissance %</t>
+        </is>
+      </c>
+      <c r="D139" s="29" t="inlineStr">
         <is>
           <t>Gain abonnes</t>
         </is>
       </c>
-      <c r="H102" s="29" t="inlineStr">
+    </row>
+    <row r="140">
+      <c r="A140" s="61" t="n">
+        <v>1</v>
+      </c>
+      <c r="B140" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C140" s="34" t="n">
+        <v>0.4954451014863359</v>
+      </c>
+      <c r="D140" s="32" t="n">
+        <v>3100</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B141" s="63" t="inlineStr">
+        <is>
+          <t>David Lisnard</t>
+        </is>
+      </c>
+      <c r="C141" s="34" t="n">
+        <v>0.4171011470281538</v>
+      </c>
+      <c r="D141" s="32" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B142" s="63" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C142" s="34" t="n">
+        <v>0.1395673412421417</v>
+      </c>
+      <c r="D142" s="32" t="n">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B143" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C143" s="34" t="n">
+        <v>0.046904315197005</v>
+      </c>
+      <c r="D143" s="32" t="n">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B144" s="63" t="inlineStr">
+        <is>
+          <t>Édouard Philippe</t>
+        </is>
+      </c>
+      <c r="C144" s="34" t="n">
+        <v>0.03187420314492151</v>
+      </c>
+      <c r="D144" s="32" t="n">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B145" s="63" t="inlineStr">
+        <is>
+          <t>Jean-Luc Mélenchon</t>
+        </is>
+      </c>
+      <c r="C145" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D145" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B146" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C146" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D146" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B147" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C147" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D147" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B148" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C148" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D148" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B149" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C149" s="41" t="n">
+        <v>-0.03247807729782615</v>
+      </c>
+      <c r="D149" s="40" t="n">
+        <v>-100</v>
+      </c>
+    </row>
+    <row r="151" ht="20" customHeight="1">
+      <c r="A151" s="27" t="inlineStr">
+        <is>
+          <t>FACEBOOK - 7 JOURS</t>
+        </is>
+      </c>
+      <c r="B151" s="28" t="n"/>
+      <c r="C151" s="28" t="n"/>
+      <c r="D151" s="28" t="n"/>
+    </row>
+    <row r="152" ht="30" customHeight="1">
+      <c r="A152" s="29" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B152" s="29" t="inlineStr">
+        <is>
+          <t>PERSONNE</t>
+        </is>
+      </c>
+      <c r="C152" s="29" t="inlineStr">
         <is>
           <t>Croissance %</t>
         </is>
       </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="61" t="n">
+      <c r="D152" s="29" t="inlineStr">
+        <is>
+          <t>Gain abonnes</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="61" t="n">
         <v>1</v>
       </c>
-      <c r="B103" s="45" t="inlineStr">
+      <c r="B153" s="63" t="inlineStr">
         <is>
           <t>David Lisnard</t>
         </is>
       </c>
-      <c r="C103" s="34" t="n">
-        <v>1.523211931068968</v>
-      </c>
-      <c r="D103" s="32" t="n">
-        <v>8375</v>
-      </c>
-      <c r="F103" s="45" t="inlineStr">
+      <c r="C153" s="34" t="n">
+        <v>3.409090909090917</v>
+      </c>
+      <c r="D153" s="32" t="n">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="61" t="n">
+        <v>2</v>
+      </c>
+      <c r="B154" s="63" t="inlineStr">
+        <is>
+          <t>Gabriel Attal</t>
+        </is>
+      </c>
+      <c r="C154" s="34" t="n">
+        <v>2.840909090909083</v>
+      </c>
+      <c r="D154" s="32" t="n">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="61" t="n">
+        <v>3</v>
+      </c>
+      <c r="B155" s="63" t="inlineStr">
+        <is>
+          <t>Marine Tondelier</t>
+        </is>
+      </c>
+      <c r="C155" s="34" t="n">
+        <v>1.249999999999996</v>
+      </c>
+      <c r="D155" s="32" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="62" t="n">
+        <v>4</v>
+      </c>
+      <c r="B156" s="63" t="inlineStr">
+        <is>
+          <t>Raphaël Glucksmann</t>
+        </is>
+      </c>
+      <c r="C156" s="34" t="n">
+        <v>0.5555555555555536</v>
+      </c>
+      <c r="D156" s="32" t="n">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="62" t="n">
+        <v>5</v>
+      </c>
+      <c r="B157" s="63" t="inlineStr">
+        <is>
+          <t>Bruno Retailleau</t>
+        </is>
+      </c>
+      <c r="C157" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D157" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="62" t="n">
+        <v>6</v>
+      </c>
+      <c r="B158" s="63" t="inlineStr">
         <is>
           <t>Jean-Luc Mélenchon</t>
         </is>
       </c>
-      <c r="G103" s="32" t="n">
-        <v>8859</v>
-      </c>
-      <c r="H103" s="34" t="n">
-        <v>0.165956650451915</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="61" t="n">
-        <v>2</v>
-      </c>
-      <c r="B104" s="45" t="inlineStr">
-        <is>
-          <t>Gabriel Attal</t>
-        </is>
-      </c>
-      <c r="C104" s="34" t="n">
-        <v>0.3150103940676496</v>
-      </c>
-      <c r="D104" s="32" t="n">
-        <v>4446</v>
-      </c>
-      <c r="F104" s="45" t="inlineStr">
-        <is>
-          <t>David Lisnard</t>
-        </is>
-      </c>
-      <c r="G104" s="32" t="n">
-        <v>8375</v>
-      </c>
-      <c r="H104" s="34" t="n">
-        <v>1.523211931068968</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="61" t="n">
-        <v>3</v>
-      </c>
-      <c r="B105" s="45" t="inlineStr">
-        <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="C105" s="34" t="n">
-        <v>0.1700454386578176</v>
-      </c>
-      <c r="D105" s="32" t="n">
-        <v>973</v>
-      </c>
-      <c r="F105" s="45" t="inlineStr">
-        <is>
-          <t>Gabriel Attal</t>
-        </is>
-      </c>
-      <c r="G105" s="32" t="n">
-        <v>4446</v>
-      </c>
-      <c r="H105" s="34" t="n">
-        <v>0.3150103940676496</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="62" t="n">
-        <v>4</v>
-      </c>
-      <c r="B106" s="63" t="inlineStr">
-        <is>
-          <t>Jean-Luc Mélenchon</t>
-        </is>
-      </c>
-      <c r="C106" s="34" t="n">
-        <v>0.165956650451915</v>
-      </c>
-      <c r="D106" s="32" t="n">
-        <v>8859</v>
-      </c>
-      <c r="F106" s="63" t="inlineStr">
+      <c r="C158" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D158" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="62" t="n">
+        <v>7</v>
+      </c>
+      <c r="B159" s="63" t="inlineStr">
+        <is>
+          <t>Jordan Bardella</t>
+        </is>
+      </c>
+      <c r="C159" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D159" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="62" t="n">
+        <v>8</v>
+      </c>
+      <c r="B160" s="63" t="inlineStr">
+        <is>
+          <t>Marine Le Pen</t>
+        </is>
+      </c>
+      <c r="C160" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D160" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="62" t="n">
+        <v>9</v>
+      </c>
+      <c r="B161" s="63" t="inlineStr">
+        <is>
+          <t>Xavier Bertrand</t>
+        </is>
+      </c>
+      <c r="C161" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D161" s="53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="62" t="n">
+        <v>10</v>
+      </c>
+      <c r="B162" s="63" t="inlineStr">
         <is>
           <t>Édouard Philippe</t>
         </is>
       </c>
-      <c r="G106" s="32" t="n">
-        <v>1374</v>
-      </c>
-      <c r="H106" s="34" t="n">
-        <v>0.07406804449041626</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" s="62" t="n">
-        <v>5</v>
-      </c>
-      <c r="B107" s="63" t="inlineStr">
-        <is>
-          <t>Bruno Retailleau</t>
-        </is>
-      </c>
-      <c r="C107" s="34" t="n">
-        <v>0.1020198345538903</v>
-      </c>
-      <c r="D107" s="32" t="n">
-        <v>516</v>
-      </c>
-      <c r="F107" s="63" t="inlineStr">
-        <is>
-          <t>Marine Tondelier</t>
-        </is>
-      </c>
-      <c r="G107" s="32" t="n">
-        <v>973</v>
-      </c>
-      <c r="H107" s="34" t="n">
-        <v>0.1700454386578176</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="62" t="n">
-        <v>6</v>
-      </c>
-      <c r="B108" s="63" t="inlineStr">
-        <is>
-          <t>Édouard Philippe</t>
-        </is>
-      </c>
-      <c r="C108" s="34" t="n">
-        <v>0.07406804449041626</v>
-      </c>
-      <c r="D108" s="32" t="n">
-        <v>1374</v>
-      </c>
-      <c r="F108" s="63" t="inlineStr">
-        <is>
-          <t>Bruno Retailleau</t>
-        </is>
-      </c>
-      <c r="G108" s="32" t="n">
-        <v>516</v>
-      </c>
-      <c r="H108" s="34" t="n">
-        <v>0.1020198345538903</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" s="62" t="n">
-        <v>7</v>
-      </c>
-      <c r="B109" s="63" t="inlineStr">
-        <is>
-          <t>Raphaël Glucksmann</t>
-        </is>
-      </c>
-      <c r="C109" s="34" t="n">
-        <v>0.03397313098865151</v>
-      </c>
-      <c r="D109" s="32" t="n">
-        <v>382</v>
-      </c>
-      <c r="F109" s="63" t="inlineStr">
-        <is>
-          <t>Marine Le Pen</t>
-        </is>
-      </c>
-      <c r="G109" s="32" t="n">
-        <v>472</v>
-      </c>
-      <c r="H109" s="34" t="n">
-        <v>0.008059027596374335</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="62" t="n">
-        <v>8</v>
-      </c>
-      <c r="B110" s="63" t="inlineStr">
-        <is>
-          <t>Marine Le Pen</t>
-        </is>
-      </c>
-      <c r="C110" s="34" t="n">
-        <v>0.008059027596374335</v>
-      </c>
-      <c r="D110" s="32" t="n">
-        <v>472</v>
-      </c>
-      <c r="F110" s="63" t="inlineStr">
-        <is>
-          <t>Raphaël Glucksmann</t>
-        </is>
-      </c>
-      <c r="G110" s="32" t="n">
-        <v>382</v>
-      </c>
-      <c r="H110" s="34" t="n">
-        <v>0.03397313098865151</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="62" t="n">
-        <v>9</v>
-      </c>
-      <c r="B111" s="63" t="inlineStr">
-        <is>
-          <t>Jordan Bardella</t>
-        </is>
-      </c>
-      <c r="C111" s="34" t="n">
-        <v>0.005203708137635488</v>
-      </c>
-      <c r="D111" s="32" t="n">
-        <v>168</v>
-      </c>
-      <c r="F111" s="63" t="inlineStr">
-        <is>
-          <t>Jordan Bardella</t>
-        </is>
-      </c>
-      <c r="G111" s="32" t="n">
-        <v>168</v>
-      </c>
-      <c r="H111" s="34" t="n">
-        <v>0.005203708137635488</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" s="62" t="n">
-        <v>10</v>
-      </c>
-      <c r="B112" s="63" t="inlineStr">
-        <is>
-          <t>Xavier Bertrand</t>
-        </is>
-      </c>
-      <c r="C112" s="41" t="n">
-        <v>-0.005371242368357176</v>
-      </c>
-      <c r="D112" s="40" t="n">
-        <v>-18</v>
-      </c>
-      <c r="F112" s="63" t="inlineStr">
-        <is>
-          <t>Xavier Bertrand</t>
-        </is>
-      </c>
-      <c r="G112" s="40" t="n">
-        <v>-18</v>
-      </c>
-      <c r="H112" s="41" t="n">
-        <v>-0.005371242368357176</v>
+      <c r="C162" s="54" t="n">
+        <v>0</v>
+      </c>
+      <c r="D162" s="53" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -8499,7 +9434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BG7"/>
+  <dimension ref="A1:BG8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8813,13 +9748,13 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>505784</v>
+        <v>436784</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>549825</v>
+        <v>448825</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>1411382</v>
+        <v>924382</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>5338141</v>
@@ -8840,7 +9775,7 @@
         <v>335118</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>1855051</v>
+        <v>1425051</v>
       </c>
       <c r="M3" t="inlineStr">
         <is>
@@ -8960,13 +9895,13 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>506200</v>
+        <v>437200</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>546800</v>
+        <v>445800</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>1412380</v>
+        <v>925380</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>5340366</v>
@@ -8987,7 +9922,7 @@
         <v>335113</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>1855114</v>
+        <v>1425114</v>
       </c>
       <c r="M4" t="inlineStr">
         <is>
@@ -8995,13 +9930,13 @@
         </is>
       </c>
       <c r="N4" s="14" t="n">
-        <v>1000.82</v>
+        <v>1000.95</v>
       </c>
       <c r="O4" s="14" t="n">
-        <v>994.5</v>
+        <v>993.26</v>
       </c>
       <c r="P4" s="14" t="n">
-        <v>1000.71</v>
+        <v>1001.08</v>
       </c>
       <c r="Q4" s="14" t="n">
         <v>1000.42</v>
@@ -9022,7 +9957,7 @@
         <v>999.99</v>
       </c>
       <c r="W4" s="14" t="n">
-        <v>1000.03</v>
+        <v>1000.04</v>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
@@ -9106,16 +10041,37 @@
           <t>02/09/2026</t>
         </is>
       </c>
+      <c r="B5" s="2" t="n">
+        <v>437300</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>452603</v>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>926700</v>
+      </c>
       <c r="G5" s="2" t="n">
         <v>5857000</v>
       </c>
       <c r="J5" s="2" t="n">
         <v>335400</v>
       </c>
+      <c r="K5" s="2" t="n">
+        <v>1425300</v>
+      </c>
       <c r="M5" t="inlineStr">
         <is>
           <t>02/09/2026</t>
         </is>
+      </c>
+      <c r="N5" s="14" t="n">
+        <v>1001.18</v>
+      </c>
+      <c r="O5" s="14" t="n">
+        <v>1008.42</v>
+      </c>
+      <c r="P5" s="14" t="n">
+        <v>1002.51</v>
       </c>
       <c r="S5" s="14" t="n">
         <v>1000.04</v>
@@ -9123,6 +10079,9 @@
       <c r="V5" s="14" t="n">
         <v>1000.84</v>
       </c>
+      <c r="W5" s="14" t="n">
+        <v>1000.17</v>
+      </c>
       <c r="Y5" t="inlineStr">
         <is>
           <t>02/09/2026</t>
@@ -9226,8 +10185,14 @@
           <t>03/09/2026</t>
         </is>
       </c>
+      <c r="B6" s="2" t="n">
+        <v>437010</v>
+      </c>
       <c r="C6" s="2" t="n">
-        <v>557201</v>
+        <v>456201</v>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>928884</v>
       </c>
       <c r="E6" s="2" t="n">
         <v>5347736</v>
@@ -9248,15 +10213,21 @@
         <v>335130</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>1856332</v>
+        <v>1425332</v>
       </c>
       <c r="M6" t="inlineStr">
         <is>
           <t>03/09/2026</t>
         </is>
       </c>
+      <c r="N6" s="14" t="n">
+        <v>1000.52</v>
+      </c>
       <c r="O6" s="14" t="n">
-        <v>1013.42</v>
+        <v>1016.43</v>
+      </c>
+      <c r="P6" s="14" t="n">
+        <v>1004.87</v>
       </c>
       <c r="Q6" s="14" t="n">
         <v>1001.8</v>
@@ -9277,7 +10248,7 @@
         <v>1000.04</v>
       </c>
       <c r="W6" s="14" t="n">
-        <v>1000.69</v>
+        <v>1000.2</v>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
@@ -9383,13 +10354,13 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>506300</v>
+        <v>437300</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>558200</v>
+        <v>456200</v>
       </c>
       <c r="D7" s="2" t="n">
-        <v>1415828</v>
+        <v>928828</v>
       </c>
       <c r="E7" s="2" t="n">
         <v>5347000</v>
@@ -9410,7 +10381,7 @@
         <v>335100</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>1856425</v>
+        <v>1425425</v>
       </c>
       <c r="M7" t="inlineStr">
         <is>
@@ -9418,13 +10389,13 @@
         </is>
       </c>
       <c r="N7" s="14" t="n">
-        <v>1001.02</v>
+        <v>1001.18</v>
       </c>
       <c r="O7" s="14" t="n">
-        <v>1015.23</v>
+        <v>1016.43</v>
       </c>
       <c r="P7" s="14" t="n">
-        <v>1003.15</v>
+        <v>1004.81</v>
       </c>
       <c r="Q7" s="14" t="n">
         <v>1001.66</v>
@@ -9445,7 +10416,7 @@
         <v>999.95</v>
       </c>
       <c r="W7" s="14" t="n">
-        <v>1000.74</v>
+        <v>1000.26</v>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
@@ -9542,6 +10513,174 @@
       </c>
       <c r="BD7" s="14" t="n">
         <v>1005.88</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>437300</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>466600</v>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>930000</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>5367000</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>2828800</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>5858000</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>574200</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>1125800</v>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>335400</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>1425500</v>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="N8" s="14" t="n">
+        <v>1001.18</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <v>1039.6</v>
+      </c>
+      <c r="P8" s="14" t="n">
+        <v>1006.08</v>
+      </c>
+      <c r="Q8" s="14" t="n">
+        <v>1005.41</v>
+      </c>
+      <c r="R8" s="14" t="n">
+        <v>876.21</v>
+      </c>
+      <c r="S8" s="14" t="n">
+        <v>1000.21</v>
+      </c>
+      <c r="T8" s="14" t="n">
+        <v>1003.5</v>
+      </c>
+      <c r="U8" s="14" t="n">
+        <v>1001.23</v>
+      </c>
+      <c r="V8" s="14" t="n">
+        <v>1000.84</v>
+      </c>
+      <c r="W8" s="14" t="n">
+        <v>1000.32</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="Z8" s="14" t="n">
+        <v>1003.94</v>
+      </c>
+      <c r="AA8" s="14" t="n">
+        <v>1082.68</v>
+      </c>
+      <c r="AB8" s="14" t="n">
+        <v>1000.47</v>
+      </c>
+      <c r="AC8" s="14" t="n">
+        <v>1034.43</v>
+      </c>
+      <c r="AD8" s="14" t="n">
+        <v>712.88</v>
+      </c>
+      <c r="AE8" s="14" t="n">
+        <v>1001.6</v>
+      </c>
+      <c r="AF8" s="14" t="n">
+        <v>1002.81</v>
+      </c>
+      <c r="AG8" s="14" t="n">
+        <v>1000.76</v>
+      </c>
+      <c r="AH8" s="14" t="n">
+        <v>1009.18</v>
+      </c>
+      <c r="AI8" s="14" t="n">
+        <v>1000.68</v>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="AL8" s="14" t="n">
+        <v>1000.47</v>
+      </c>
+      <c r="AM8" s="14" t="n">
+        <v>1004.17</v>
+      </c>
+      <c r="AN8" s="14" t="n">
+        <v>1001.4</v>
+      </c>
+      <c r="AO8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP8" s="14" t="n">
+        <v>1004.95</v>
+      </c>
+      <c r="AQ8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS8" s="14" t="n">
+        <v>999.6799999999999</v>
+      </c>
+      <c r="AT8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AU8" s="14" t="n">
+        <v>1000.32</v>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>07/09/2026</t>
+        </is>
+      </c>
+      <c r="AX8" s="14" t="n">
+        <v>1001.18</v>
+      </c>
+      <c r="AY8" s="14" t="n">
+        <v>1060.11</v>
+      </c>
+      <c r="AZ8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BA8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BB8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BC8" s="14" t="n">
+        <v>1000</v>
+      </c>
+      <c r="BD8" s="14" t="n">
+        <v>1007.06</v>
       </c>
     </row>
   </sheetData>
